--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129152698</v>
       </c>
       <c r="B2" t="n">
-        <v>92234</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,6 +786,606 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113899903</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jägaretorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>456108</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6216804</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113899904</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jägaretorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>456101</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6216749</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113899905</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jägaretorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>456099</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6216781</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113899906</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jägaretorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456099</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6216764</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113899908</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jägaretorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456097</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6216739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Alight - NVI Karsholm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25762-2024 artfynd.xlsx
+++ b/artfynd/A 25762-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129152698</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899903</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,8 +1416,21 @@
           <t>Alight - NVI Karsholm</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113899908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>